--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -43122,12 +43122,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -43161,81 +43161,100 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O245" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R245" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.01868976085656669</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43262,17 +43281,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -43297,7 +43316,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -43306,81 +43325,175 @@
         </is>
       </c>
       <c r="N246" t="n">
+        <v>2</v>
+      </c>
+      <c r="O246" t="n">
+        <v>2</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>Invasiv meningokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN246" t="b">
         <v>1</v>
       </c>
-      <c r="O246" t="n">
-        <v>1</v>
-      </c>
-      <c r="R246" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR246" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43412,12 +43525,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -43442,7 +43555,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -43451,93 +43564,81 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O247" t="n">
-        <v>0</v>
-      </c>
-      <c r="P247" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA247" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ247" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr"/>
       <c r="AT247" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43564,17 +43665,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -43608,173 +43709,81 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O248" t="n">
-        <v>0</v>
-      </c>
-      <c r="P248" t="n">
-        <v>0</v>
-      </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W248" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X248" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD248" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE248" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF248" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG248" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ248" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK248" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM248" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN248" t="b">
         <v>1</v>
       </c>
+      <c r="R248" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ248" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43806,12 +43815,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -43836,7 +43845,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -43845,81 +43854,93 @@
         </is>
       </c>
       <c r="N249" t="n">
+        <v>0</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="n">
+        <v>0</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP249" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT249" t="n">
         <v>2</v>
       </c>
-      <c r="O249" t="n">
-        <v>2</v>
-      </c>
-      <c r="R249" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO249" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP249" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
-      <c r="AT249" t="n">
-        <v>0</v>
-      </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43946,17 +43967,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -43981,7 +44002,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -43990,81 +44011,173 @@
         </is>
       </c>
       <c r="N250" t="n">
+        <v>0</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" t="n">
+        <v>0</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
         <v>1</v>
       </c>
-      <c r="O250" t="n">
-        <v>1</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44096,12 +44209,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -44126,7 +44239,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -44135,93 +44248,81 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O251" t="n">
-        <v>0</v>
-      </c>
-      <c r="P251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R251" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ251" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44248,17 +44349,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44292,173 +44393,81 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O252" t="n">
-        <v>0</v>
-      </c>
-      <c r="P252" t="n">
-        <v>0</v>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V252" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X252" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y252" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD252" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE252" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF252" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG252" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH252" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI252" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ252" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK252" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM252" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN252" t="b">
         <v>1</v>
       </c>
+      <c r="R252" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ252" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44490,12 +44499,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -44520,7 +44529,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -44534,6 +44543,9 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
+      <c r="P253" t="n">
+        <v>0</v>
+      </c>
       <c r="R253" t="n">
         <v>0</v>
       </c>
@@ -44542,68 +44554,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44630,7 +44651,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -44665,7 +44686,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -44674,26 +44695,106 @@
         </is>
       </c>
       <c r="N254" t="n">
+        <v>0</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>0</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
         <v>1</v>
-      </c>
-      <c r="O254" t="n">
-        <v>1</v>
-      </c>
-      <c r="P254" t="n">
-        <v>1</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
@@ -44787,17 +44888,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44831,173 +44932,81 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
-        <v>1</v>
-      </c>
-      <c r="P255" t="n">
-        <v>1</v>
-      </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA255" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R255" t="n">
+        <v>0</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ255" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45029,12 +45038,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45059,7 +45068,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -45073,76 +45082,88 @@
       <c r="O256" t="n">
         <v>1</v>
       </c>
+      <c r="P256" t="n">
+        <v>1</v>
+      </c>
       <c r="R256" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45169,17 +45190,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45204,7 +45225,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -45213,81 +45234,173 @@
         </is>
       </c>
       <c r="N257" t="n">
+        <v>1</v>
+      </c>
+      <c r="O257" t="n">
+        <v>1</v>
+      </c>
+      <c r="P257" t="n">
+        <v>1</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN257" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP257" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT257" t="n">
         <v>2</v>
       </c>
-      <c r="O257" t="n">
-        <v>2</v>
-      </c>
-      <c r="R257" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO257" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP257" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr"/>
-      <c r="AT257" t="n">
-        <v>0</v>
-      </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45319,12 +45432,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45349,7 +45462,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -45358,93 +45471,81 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O258" t="n">
-        <v>0</v>
-      </c>
-      <c r="P258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ258" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45471,17 +45572,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45515,173 +45616,81 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O259" t="n">
-        <v>0</v>
-      </c>
-      <c r="P259" t="n">
-        <v>0</v>
-      </c>
-      <c r="U259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W259" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X259" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y259" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD259" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE259" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF259" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG259" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH259" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI259" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM259" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN259" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ259" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45713,12 +45722,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45743,7 +45752,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -45752,81 +45761,93 @@
         </is>
       </c>
       <c r="N260" t="n">
+        <v>0</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" t="n">
+        <v>0</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP260" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT260" t="n">
         <v>2</v>
       </c>
-      <c r="O260" t="n">
-        <v>2</v>
-      </c>
-      <c r="R260" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S260" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO260" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP260" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr"/>
-      <c r="AT260" t="n">
-        <v>0</v>
-      </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45853,17 +45874,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -45888,90 +45909,182 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N261" t="n">
+        <v>0</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" t="n">
+        <v>0</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN261" t="b">
         <v>1</v>
       </c>
-      <c r="O261" t="n">
-        <v>1</v>
-      </c>
-      <c r="R261" t="n">
-        <v>0.00367281181951979</v>
-      </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46003,12 +46116,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -46033,109 +46146,90 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R262" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AA262" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ262" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR262" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr"/>
       <c r="AT262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46162,17 +46256,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46206,175 +46300,81 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O263" t="n">
-        <v>0</v>
-      </c>
-      <c r="U263" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="V263" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W263" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X263" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y263" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA263" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD263" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr"/>
+      <c r="AT263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV263" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE263" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF263" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG263" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH263" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI263" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ263" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK263" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM263" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN263" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO263" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP263" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ263" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR263" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AT263" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU263" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV263" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46458,68 +46458,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR264" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46546,17 +46565,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46595,17 +46614,34 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="R265" t="n">
-        <v>0</v>
-      </c>
-      <c r="S265" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U265" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -46613,6 +46649,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM265" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN265" t="b">
+        <v>1</v>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46625,7 +46719,7 @@
       </c>
       <c r="AQ265" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR265" t="inlineStr">
@@ -46635,7 +46729,7 @@
       </c>
       <c r="AS265" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT265" t="n">
@@ -46643,47 +46737,47 @@
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46710,217 +46804,526 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N266" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO266" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP266" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr"/>
+      <c r="AT266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU266" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV266" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA266" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB266" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC266" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N267" t="n">
+        <v>0</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV267" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA267" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB267" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC267" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
+      <c r="F268" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
+      <c r="G268" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>D110</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>Meningococcal disease</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
         <is>
           <t>脑膜炎球菌病</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
+      <c r="K268" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr">
+      <c r="L268" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M266" t="inlineStr">
+      <c r="M268" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N266" t="n">
-        <v>0</v>
-      </c>
-      <c r="O266" t="n">
-        <v>0</v>
-      </c>
-      <c r="U266" t="inlineStr">
+      <c r="N268" t="n">
+        <v>0</v>
+      </c>
+      <c r="O268" t="n">
+        <v>0</v>
+      </c>
+      <c r="U268" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
-      <c r="V266" t="inlineStr">
+      <c r="V268" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
-      <c r="W266" t="inlineStr">
+      <c r="W268" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X266" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>Syst. meningokokksykdom</t>
         </is>
       </c>
-      <c r="Y266" t="inlineStr">
+      <c r="Y268" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z266" t="inlineStr">
+      <c r="Z268" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA266" t="inlineStr">
+      <c r="AA268" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB266" t="inlineStr">
+      <c r="AB268" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC266" t="inlineStr">
+      <c r="AC268" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD266" t="inlineStr">
+      <c r="AD268" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE266" t="inlineStr">
+      <c r="AE268" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF266" t="inlineStr">
+      <c r="AF268" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG266" t="inlineStr">
+      <c r="AG268" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH266" t="inlineStr">
+      <c r="AH268" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI266" t="inlineStr">
+      <c r="AI268" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ266" t="inlineStr">
+      <c r="AJ268" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK266" t="inlineStr">
+      <c r="AK268" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
         </is>
       </c>
-      <c r="AM266" t="inlineStr">
+      <c r="AM268" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN266" t="b">
+      <c r="AN268" t="b">
         <v>1</v>
       </c>
-      <c r="AO266" t="inlineStr">
+      <c r="AO268" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP266" t="inlineStr">
+      <c r="AP268" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ266" t="inlineStr">
+      <c r="AQ268" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR266" t="inlineStr">
+      <c r="AR268" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS266" t="inlineStr">
+      <c r="AS268" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
-      <c r="AT266" t="n">
+      <c r="AT268" t="n">
         <v>2</v>
       </c>
-      <c r="AU266" t="inlineStr">
+      <c r="AU268" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV266" t="inlineStr">
+      <c r="AV268" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW266" t="inlineStr">
+      <c r="AW268" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX266" t="inlineStr">
+      <c r="AX268" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY266" t="inlineStr">
+      <c r="AY268" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ266" t="inlineStr">
+      <c r="AZ268" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA266" t="inlineStr">
+      <c r="BA268" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB266" t="inlineStr">
+      <c r="BB268" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC266" t="inlineStr">
+      <c r="BC268" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47042,7 +47445,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -47052,7 +47455,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -47072,7 +47475,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -47104,7 +47507,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -41355,13 +41355,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O234" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R234" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.04774655365375727</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -46261,12 +46261,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46291,22 +46291,22 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>0.00367281181951979</v>
+        <v>0</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -46339,42 +46339,42 @@
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46445,100 +46445,81 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R264" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AA264" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ264" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR264" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr"/>
       <c r="AT264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46565,7 +46546,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -46614,98 +46595,23 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
+      <c r="R265" t="n">
+        <v>0</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U265" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
-      <c r="V265" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W265" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X265" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y265" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD265" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE265" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF265" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG265" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ265" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK265" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM265" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN265" t="b">
-        <v>1</v>
       </c>
       <c r="AO265" t="inlineStr">
         <is>
@@ -46804,17 +46710,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46853,76 +46759,170 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
-      <c r="R266" t="n">
-        <v>0</v>
-      </c>
-      <c r="S266" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ266" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK266" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM266" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN266" t="b">
+        <v>1</v>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR266" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46954,12 +46954,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -47006,87 +47006,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR267" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -47113,7 +47094,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -47162,98 +47143,23 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
+      <c r="R268" t="n">
+        <v>0</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U268" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W268" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X268" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y268" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD268" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE268" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF268" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG268" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI268" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ268" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK268" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM268" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN268" t="b">
-        <v>1</v>
       </c>
       <c r="AO268" t="inlineStr">
         <is>
@@ -47324,6 +47230,245 @@
         </is>
       </c>
       <c r="BC268" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N269" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN269" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT269" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU269" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV269" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA269" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB269" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC269" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47445,7 +47590,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -47455,7 +47600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -47507,7 +47652,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -42171,12 +42171,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -42210,100 +42210,84 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O240" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>1</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>0.0007785328272632622</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR240" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -42330,7 +42314,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -42379,98 +42363,23 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U241" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
-        <v>1</v>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
@@ -42569,17 +42478,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -42613,81 +42522,175 @@
         </is>
       </c>
       <c r="N242" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
         <v>1</v>
       </c>
-      <c r="O242" t="n">
-        <v>1</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR242" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42719,12 +42722,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -42764,94 +42767,75 @@
         <v>1</v>
       </c>
       <c r="R243" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ243" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR243" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -42878,7 +42862,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -42927,98 +42911,23 @@
       <c r="O244" t="n">
         <v>1</v>
       </c>
+      <c r="R244" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U244" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN244" t="b">
-        <v>1</v>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
@@ -43117,17 +43026,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -43161,22 +43070,39 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O245" t="n">
-        <v>2</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0.01868976085656669</v>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -43184,6 +43110,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN245" t="b">
+        <v>1</v>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -43206,7 +43190,7 @@
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -43219,42 +43203,42 @@
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43281,7 +43265,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -43330,98 +43314,23 @@
       <c r="O246" t="n">
         <v>2</v>
       </c>
+      <c r="R246" t="n">
+        <v>0.01868976085656669</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U246" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
-        </is>
-      </c>
-      <c r="W246" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X246" t="inlineStr">
-        <is>
-          <t>Invasiv meningokockinfektion</t>
-        </is>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD246" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE246" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF246" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG246" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ246" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK246" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
-        </is>
-      </c>
-      <c r="AM246" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN246" t="b">
-        <v>1</v>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
@@ -43520,17 +43429,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -43564,81 +43473,175 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O247" t="n">
-        <v>6</v>
-      </c>
-      <c r="R247" t="n">
-        <v>0.001719022879661631</v>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>Invasiv meningokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN247" t="b">
+        <v>1</v>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43670,12 +43673,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -43700,7 +43703,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -43709,13 +43712,13 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O248" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R248" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -43748,42 +43751,42 @@
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43815,12 +43818,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -43854,93 +43857,81 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O249" t="n">
-        <v>0</v>
-      </c>
-      <c r="P249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA249" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ249" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr"/>
       <c r="AT249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43958,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -44019,98 +44010,18 @@
       <c r="P250" t="n">
         <v>0</v>
       </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R250" t="n">
+        <v>0</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD250" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE250" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF250" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG250" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH250" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ250" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK250" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM250" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN250" t="b">
-        <v>1</v>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
@@ -44204,17 +44115,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -44239,7 +44150,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -44248,81 +44159,173 @@
         </is>
       </c>
       <c r="N251" t="n">
+        <v>0</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+      <c r="P251" t="n">
+        <v>0</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT251" t="n">
         <v>2</v>
       </c>
-      <c r="O251" t="n">
-        <v>2</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO251" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP251" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr"/>
-      <c r="AT251" t="n">
-        <v>0</v>
-      </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44354,12 +44357,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44384,7 +44387,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -44393,13 +44396,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R252" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -44432,42 +44435,42 @@
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44499,12 +44502,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -44538,93 +44541,81 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O253" t="n">
-        <v>0</v>
-      </c>
-      <c r="P253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA253" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ253" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr"/>
       <c r="AT253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44651,7 +44642,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -44703,98 +44694,18 @@
       <c r="P254" t="n">
         <v>0</v>
       </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V254" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W254" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X254" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y254" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z254" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R254" t="n">
+        <v>0</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD254" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE254" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF254" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG254" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH254" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI254" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM254" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN254" t="b">
-        <v>1</v>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
@@ -44888,17 +44799,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44923,7 +44834,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -44937,76 +44848,168 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="R255" t="n">
-        <v>0</v>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P255" t="n">
+        <v>0</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN255" t="b">
+        <v>1</v>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR255" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45038,12 +45041,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45077,93 +45080,81 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O256" t="n">
-        <v>1</v>
-      </c>
-      <c r="P256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ256" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45190,7 +45181,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -45242,98 +45233,18 @@
       <c r="P257" t="n">
         <v>1</v>
       </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R257" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN257" t="b">
-        <v>1</v>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
@@ -45427,17 +45338,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45462,7 +45373,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -45476,76 +45387,168 @@
       <c r="O258" t="n">
         <v>1</v>
       </c>
-      <c r="R258" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P258" t="n">
+        <v>1</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN258" t="b">
+        <v>1</v>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45577,12 +45580,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45607,7 +45610,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -45616,13 +45619,13 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R259" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -45655,42 +45658,42 @@
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45722,12 +45725,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45761,93 +45764,81 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O260" t="n">
-        <v>0</v>
-      </c>
-      <c r="P260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA260" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ260" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45874,7 +45865,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -45926,98 +45917,18 @@
       <c r="P261" t="n">
         <v>0</v>
       </c>
-      <c r="U261" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V261" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W261" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X261" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y261" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R261" t="n">
+        <v>0</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD261" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE261" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF261" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG261" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH261" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI261" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ261" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK261" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM261" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN261" t="b">
-        <v>1</v>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
@@ -46111,17 +46022,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -46146,7 +46057,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -46155,81 +46066,173 @@
         </is>
       </c>
       <c r="N262" t="n">
+        <v>0</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
+      <c r="P262" t="n">
+        <v>0</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN262" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT262" t="n">
         <v>2</v>
       </c>
-      <c r="O262" t="n">
-        <v>2</v>
-      </c>
-      <c r="R262" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S262" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO262" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP262" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR262" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr"/>
-      <c r="AT262" t="n">
-        <v>0</v>
-      </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46261,12 +46264,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46291,7 +46294,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -46300,13 +46303,13 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O263" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R263" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -46339,42 +46342,42 @@
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46406,12 +46409,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46436,22 +46439,22 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>0.00367281181951979</v>
+        <v>0</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -46484,42 +46487,42 @@
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46551,12 +46554,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46581,12 +46584,12 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N265" t="n">
@@ -46595,6 +46598,9 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -46603,14 +46609,9 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO265" t="inlineStr">
@@ -46620,22 +46621,17 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ265" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR265" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS265" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
         </is>
       </c>
       <c r="AT265" t="n">
@@ -46643,47 +46639,47 @@
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46715,12 +46711,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46745,12 +46741,12 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N266" t="n">
@@ -46759,24 +46755,27 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
         </is>
       </c>
       <c r="V266" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
         </is>
       </c>
       <c r="W266" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X266" t="inlineStr">
         <is>
-          <t>Meningococcus, total</t>
+          <t>Meningococcal Infection</t>
         </is>
       </c>
       <c r="Y266" t="inlineStr">
@@ -46786,12 +46785,12 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB266" t="inlineStr">
@@ -46801,7 +46800,7 @@
       </c>
       <c r="AC266" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD266" t="inlineStr">
@@ -46836,12 +46835,12 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM266" t="inlineStr">
@@ -46859,22 +46858,17 @@
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ266" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR266" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS266" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
         </is>
       </c>
       <c r="AT266" t="n">
@@ -46882,47 +46876,47 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46954,12 +46948,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -46993,13 +46987,13 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R267" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -47032,42 +47026,42 @@
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47099,12 +47093,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -47153,7 +47147,7 @@
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -47173,7 +47167,7 @@
       </c>
       <c r="AQ268" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR268" t="inlineStr">
@@ -47183,7 +47177,7 @@
       </c>
       <c r="AS268" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT268" t="n">
@@ -47191,47 +47185,47 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47263,12 +47257,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47309,22 +47303,22 @@
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="W269" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X269" t="inlineStr">
         <is>
-          <t>Syst. meningokokksykdom</t>
+          <t>Meningococcus, total</t>
         </is>
       </c>
       <c r="Y269" t="inlineStr">
@@ -47349,7 +47343,7 @@
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD269" t="inlineStr">
@@ -47384,17 +47378,17 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -47412,7 +47406,7 @@
       </c>
       <c r="AQ269" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR269" t="inlineStr">
@@ -47422,7 +47416,7 @@
       </c>
       <c r="AS269" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT269" t="n">
@@ -47430,45 +47424,593 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV269" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA269" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB269" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC269" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr"/>
+      <c r="AT270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV270" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA270" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB270" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC270" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="R271" t="n">
+        <v>0</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV269" t="inlineStr">
+      <c r="AV271" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW269" t="inlineStr">
+      <c r="AW271" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX269" t="inlineStr">
+      <c r="AX271" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY269" t="inlineStr">
+      <c r="AY271" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ269" t="inlineStr">
+      <c r="AZ271" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA269" t="inlineStr">
+      <c r="BA271" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB269" t="inlineStr">
+      <c r="BB271" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC269" t="inlineStr">
+      <c r="BC271" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>0</v>
+      </c>
+      <c r="O272" t="n">
+        <v>0</v>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN272" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV272" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA272" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB272" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC272" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47590,7 +48132,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10">
@@ -47600,7 +48142,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -47620,7 +48162,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -47652,7 +48194,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16">
@@ -47662,7 +48204,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -47522,13 +47522,13 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R270" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -47686,10 +47686,10 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U271" t="inlineStr">
         <is>
@@ -48584,7 +48584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -48406,6 +48406,151 @@
         </is>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" t="n">
+        <v>0</v>
+      </c>
+      <c r="R275" t="n">
+        <v>0</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr"/>
+      <c r="AT275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV275" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA275" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB275" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC275" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48439,7 +48584,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -48522,7 +48667,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10">
@@ -48532,7 +48677,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -43660,12 +43660,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -43699,13 +43699,13 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O248" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R248" t="n">
-        <v>0.01868976085656669</v>
+        <v>0.2080386513119012</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -43729,7 +43729,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
@@ -43737,62 +43737,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43824,12 +43819,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -43863,29 +43858,29 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O249" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>Invasiv meningokockinfektion</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
@@ -43895,7 +43890,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -43910,7 +43905,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -43945,17 +43940,17 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+          <t>New Zealand PHF Science monthly meningococcal disease notifications.</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -43968,7 +43963,7 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
@@ -43976,62 +43971,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44063,12 +44053,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -44102,81 +44092,100 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O250" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R250" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.01868976085656669</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR250" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44203,17 +44212,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -44238,7 +44247,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -44247,81 +44256,175 @@
         </is>
       </c>
       <c r="N251" t="n">
+        <v>2</v>
+      </c>
+      <c r="O251" t="n">
+        <v>2</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Invasiv meningokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
         <v>1</v>
       </c>
-      <c r="O251" t="n">
-        <v>1</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44353,12 +44456,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44383,7 +44486,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -44392,93 +44495,81 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O252" t="n">
-        <v>0</v>
-      </c>
-      <c r="P252" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R252" t="n">
-        <v>0</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ252" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44505,17 +44596,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -44549,173 +44640,81 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O253" t="n">
-        <v>0</v>
-      </c>
-      <c r="P253" t="n">
-        <v>0</v>
-      </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA253" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN253" t="b">
         <v>1</v>
       </c>
+      <c r="R253" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ253" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr"/>
       <c r="AT253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44747,12 +44746,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44777,7 +44776,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -44786,81 +44785,93 @@
         </is>
       </c>
       <c r="N254" t="n">
+        <v>0</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>0</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT254" t="n">
         <v>2</v>
       </c>
-      <c r="O254" t="n">
-        <v>2</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP254" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr"/>
-      <c r="AT254" t="n">
-        <v>0</v>
-      </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44887,17 +44898,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44922,7 +44933,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -44931,81 +44942,173 @@
         </is>
       </c>
       <c r="N255" t="n">
+        <v>0</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="n">
+        <v>0</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN255" t="b">
         <v>1</v>
       </c>
-      <c r="O255" t="n">
-        <v>1</v>
-      </c>
-      <c r="R255" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR255" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45037,12 +45140,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45067,7 +45170,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -45076,93 +45179,81 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O256" t="n">
-        <v>0</v>
-      </c>
-      <c r="P256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ256" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45189,17 +45280,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45233,173 +45324,81 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O257" t="n">
-        <v>0</v>
-      </c>
-      <c r="P257" t="n">
-        <v>0</v>
-      </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA257" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN257" t="b">
         <v>1</v>
       </c>
+      <c r="R257" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ257" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr"/>
       <c r="AT257" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45431,12 +45430,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45461,7 +45460,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -45475,6 +45474,9 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
+      <c r="P258" t="n">
+        <v>0</v>
+      </c>
       <c r="R258" t="n">
         <v>0</v>
       </c>
@@ -45483,68 +45485,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45571,7 +45582,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -45606,7 +45617,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -45615,26 +45626,106 @@
         </is>
       </c>
       <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM259" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN259" t="b">
         <v>1</v>
-      </c>
-      <c r="O259" t="n">
-        <v>1</v>
-      </c>
-      <c r="P259" t="n">
-        <v>1</v>
-      </c>
-      <c r="R259" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S259" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
@@ -45728,17 +45819,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45772,173 +45863,81 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
-        <v>1</v>
-      </c>
-      <c r="P260" t="n">
-        <v>1</v>
-      </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA260" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD260" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE260" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF260" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG260" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ260" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK260" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM260" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN260" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ260" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45970,12 +45969,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -46000,7 +45999,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -46014,76 +46013,88 @@
       <c r="O261" t="n">
         <v>1</v>
       </c>
+      <c r="P261" t="n">
+        <v>1</v>
+      </c>
       <c r="R261" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46110,17 +46121,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -46145,7 +46156,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -46154,81 +46165,173 @@
         </is>
       </c>
       <c r="N262" t="n">
+        <v>1</v>
+      </c>
+      <c r="O262" t="n">
+        <v>1</v>
+      </c>
+      <c r="P262" t="n">
+        <v>1</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN262" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT262" t="n">
         <v>2</v>
       </c>
-      <c r="O262" t="n">
-        <v>2</v>
-      </c>
-      <c r="R262" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S262" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO262" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP262" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR262" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr"/>
-      <c r="AT262" t="n">
-        <v>0</v>
-      </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46260,12 +46363,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46290,7 +46393,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -46299,93 +46402,81 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O263" t="n">
-        <v>0</v>
-      </c>
-      <c r="P263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R263" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA263" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ263" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr"/>
       <c r="AT263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46412,17 +46503,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46456,173 +46547,81 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O264" t="n">
-        <v>0</v>
-      </c>
-      <c r="P264" t="n">
-        <v>0</v>
-      </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V264" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W264" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X264" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y264" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA264" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD264" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE264" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF264" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG264" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH264" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI264" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ264" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK264" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM264" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN264" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ264" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr"/>
       <c r="AT264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46654,12 +46653,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46684,7 +46683,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -46693,81 +46692,93 @@
         </is>
       </c>
       <c r="N265" t="n">
+        <v>0</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
+      <c r="R265" t="n">
+        <v>0</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP265" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT265" t="n">
         <v>2</v>
       </c>
-      <c r="O265" t="n">
-        <v>2</v>
-      </c>
-      <c r="R265" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S265" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO265" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP265" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR265" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr"/>
-      <c r="AT265" t="n">
-        <v>0</v>
-      </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46794,17 +46805,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46829,7 +46840,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -46843,76 +46854,168 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
-      <c r="R266" t="n">
-        <v>0</v>
-      </c>
-      <c r="S266" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ266" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK266" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM266" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN266" t="b">
+        <v>1</v>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR266" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46944,12 +47047,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -46974,7 +47077,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -46983,93 +47086,81 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O267" t="n">
-        <v>0</v>
-      </c>
-      <c r="P267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R267" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47096,17 +47187,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -47145,168 +47236,76 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="P268" t="n">
-        <v>0</v>
-      </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W268" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X268" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y268" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD268" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE268" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF268" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG268" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI268" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ268" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK268" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM268" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN268" t="b">
-        <v>1</v>
+      <c r="R268" t="n">
+        <v>0</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47338,12 +47337,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47368,90 +47367,102 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O269" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>0.00367281181951979</v>
+        <v>0</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47478,17 +47489,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47513,38 +47524,116 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN270" t="b">
         <v>1</v>
       </c>
-      <c r="O270" t="n">
-        <v>1</v>
-      </c>
-      <c r="R270" t="n">
-        <v>0.01778809170864137</v>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AA270" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47552,22 +47641,17 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ270" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS270" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1430</t>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
         </is>
       </c>
       <c r="AT270" t="n">
@@ -47575,47 +47659,47 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47642,17 +47726,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47691,170 +47775,76 @@
       <c r="O271" t="n">
         <v>1</v>
       </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="V271" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W271" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X271" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y271" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD271" t="inlineStr">
+      <c r="R271" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
+      <c r="AT271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV271" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE271" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF271" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG271" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH271" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI271" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ271" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK271" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM271" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN271" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO271" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP271" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR271" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AT271" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU271" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV271" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47886,12 +47876,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -47925,81 +47915,100 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR272" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48026,17 +48035,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -48070,22 +48079,39 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O273" t="n">
-        <v>0</v>
-      </c>
-      <c r="R273" t="n">
-        <v>0</v>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -48093,6 +48119,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -48105,7 +48189,7 @@
       </c>
       <c r="AQ273" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR273" t="inlineStr">
@@ -48115,7 +48199,7 @@
       </c>
       <c r="AS273" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
       <c r="AT273" t="n">
@@ -48123,47 +48207,47 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48190,17 +48274,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -48239,170 +48323,76 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X274" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y274" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA274" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD274" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE274" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF274" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG274" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ274" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK274" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM274" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN274" t="b">
-        <v>1</v>
+      <c r="R274" t="n">
+        <v>0</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ274" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR274" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS274" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr"/>
       <c r="AT274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -48434,118 +48424,521 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" t="n">
+        <v>0</v>
+      </c>
+      <c r="R275" t="n">
+        <v>0</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV275" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA275" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB275" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC275" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN276" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU276" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV276" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA276" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC276" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
+      <c r="G277" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>D110</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>Meningococcal disease</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
         <is>
           <t>脑膜炎球菌病</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr">
+      <c r="K277" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr">
+      <c r="L277" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M275" t="inlineStr">
+      <c r="M277" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N275" t="n">
-        <v>0</v>
-      </c>
-      <c r="O275" t="n">
-        <v>0</v>
-      </c>
-      <c r="R275" t="n">
-        <v>0</v>
-      </c>
-      <c r="S275" t="inlineStr">
+      <c r="N277" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0</v>
+      </c>
+      <c r="S277" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO275" t="inlineStr">
+      <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP275" t="inlineStr">
+      <c r="AP277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR275" t="inlineStr">
+      <c r="AR277" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS275" t="inlineStr"/>
-      <c r="AT275" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU275" t="inlineStr">
+      <c r="AS277" t="inlineStr"/>
+      <c r="AT277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU277" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV275" t="inlineStr">
+      <c r="AV277" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW275" t="inlineStr">
+      <c r="AW277" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX275" t="inlineStr">
+      <c r="AX277" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY275" t="inlineStr">
+      <c r="AY277" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ275" t="inlineStr">
+      <c r="AZ277" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA275" t="inlineStr">
+      <c r="BA277" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB275" t="inlineStr">
+      <c r="BB277" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC275" t="inlineStr">
+      <c r="BC277" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -48667,7 +49060,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -48677,7 +49070,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11">
@@ -48697,7 +49090,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -48729,7 +49122,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -48944,6 +48944,545 @@
         </is>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT278" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV278" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA278" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB278" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC278" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM279" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN279" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV279" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA279" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB279" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC279" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>4</v>
+      </c>
+      <c r="O280" t="n">
+        <v>4</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0.001146015253107754</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr"/>
+      <c r="AT280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48977,7 +49516,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -49060,7 +49599,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -49070,7 +49609,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11">
@@ -49090,7 +49629,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -49122,7 +49661,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -43112,12 +43112,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -43151,13 +43151,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R245" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -43190,42 +43190,42 @@
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -43257,12 +43257,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -43302,94 +43302,75 @@
         <v>1</v>
       </c>
       <c r="R246" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA246" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ246" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR246" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -43416,7 +43397,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -43465,98 +43446,23 @@
       <c r="O247" t="n">
         <v>1</v>
       </c>
+      <c r="R247" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U247" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W247" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD247" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE247" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF247" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG247" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ247" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK247" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM247" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN247" t="b">
-        <v>1</v>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
@@ -43655,17 +43561,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -43699,22 +43605,39 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O248" t="n">
-        <v>11</v>
-      </c>
-      <c r="R248" t="n">
-        <v>0.2080386513119012</v>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -43722,6 +43645,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -43729,7 +43710,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
@@ -43737,57 +43718,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
       <c r="AT248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43814,7 +43800,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -43863,98 +43849,23 @@
       <c r="O249" t="n">
         <v>11</v>
       </c>
+      <c r="R249" t="n">
+        <v>0.2080386513119012</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U249" t="inlineStr">
         <is>
           <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X249" t="inlineStr">
-        <is>
-          <t>Meningococcal disease</t>
-        </is>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD249" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE249" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF249" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG249" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH249" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI249" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ249" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK249" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly meningococcal disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM249" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN249" t="b">
-        <v>1</v>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
@@ -44048,17 +43959,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -44092,22 +44003,39 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O250" t="n">
-        <v>2</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0.01868976085656669</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>11</v>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -44115,6 +44043,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly meningococcal disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
+        <v>1</v>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44122,7 +44108,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -44130,62 +44116,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_MENINGOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44212,7 +44193,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -44261,98 +44242,23 @@
       <c r="O251" t="n">
         <v>2</v>
       </c>
+      <c r="R251" t="n">
+        <v>0.01868976085656669</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U251" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
         </is>
       </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>Invasiv meningokockinfektion</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN251" t="b">
-        <v>1</v>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
@@ -44451,17 +44357,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44495,81 +44401,175 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O252" t="n">
-        <v>6</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0.001719022879661631</v>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>Invasiv meningokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN252" t="b">
+        <v>1</v>
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MENINGOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44601,12 +44601,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -44631,7 +44631,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -44640,13 +44640,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O253" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R253" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -44679,42 +44679,42 @@
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44746,12 +44746,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44785,93 +44785,81 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O254" t="n">
-        <v>0</v>
-      </c>
-      <c r="P254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ254" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44898,7 +44886,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -44950,98 +44938,18 @@
       <c r="P255" t="n">
         <v>0</v>
       </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R255" t="n">
+        <v>0</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
@@ -45135,17 +45043,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45170,7 +45078,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -45179,81 +45087,173 @@
         </is>
       </c>
       <c r="N256" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>0</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM256" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN256" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT256" t="n">
         <v>2</v>
       </c>
-      <c r="O256" t="n">
-        <v>2</v>
-      </c>
-      <c r="R256" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO256" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP256" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
-      <c r="AT256" t="n">
-        <v>0</v>
-      </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45285,12 +45285,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45315,7 +45315,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -45324,13 +45324,13 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R257" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -45363,42 +45363,42 @@
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45430,12 +45430,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45469,93 +45469,81 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O258" t="n">
-        <v>0</v>
-      </c>
-      <c r="P258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ258" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45582,7 +45570,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -45634,98 +45622,18 @@
       <c r="P259" t="n">
         <v>0</v>
       </c>
-      <c r="U259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W259" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X259" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y259" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R259" t="n">
+        <v>0</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD259" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE259" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF259" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG259" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH259" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI259" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM259" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN259" t="b">
-        <v>1</v>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
@@ -45819,17 +45727,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45854,7 +45762,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -45868,76 +45776,168 @@
       <c r="O260" t="n">
         <v>0</v>
       </c>
-      <c r="R260" t="n">
-        <v>0</v>
-      </c>
-      <c r="S260" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P260" t="n">
+        <v>0</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM260" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN260" t="b">
+        <v>1</v>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45969,12 +45969,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -46008,93 +46008,81 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
-        <v>1</v>
-      </c>
-      <c r="P261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA261" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ261" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46121,7 +46109,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -46173,98 +46161,18 @@
       <c r="P262" t="n">
         <v>1</v>
       </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W262" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X262" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y262" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R262" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD262" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE262" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF262" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG262" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH262" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI262" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ262" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK262" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM262" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN262" t="b">
-        <v>1</v>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
@@ -46358,17 +46266,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46393,7 +46301,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -46407,76 +46315,168 @@
       <c r="O263" t="n">
         <v>1</v>
       </c>
-      <c r="R263" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S263" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P263" t="n">
+        <v>1</v>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN263" t="b">
+        <v>1</v>
       </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR263" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT263" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46508,12 +46508,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46538,7 +46538,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -46547,13 +46547,13 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R264" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -46586,42 +46586,42 @@
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46653,12 +46653,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46692,93 +46692,81 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O265" t="n">
-        <v>0</v>
-      </c>
-      <c r="P265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R265" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA265" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ265" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46805,7 +46793,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -46857,98 +46845,18 @@
       <c r="P266" t="n">
         <v>0</v>
       </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W266" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X266" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y266" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R266" t="n">
+        <v>0</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD266" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE266" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF266" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG266" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH266" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI266" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ266" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK266" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM266" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN266" t="b">
-        <v>1</v>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
@@ -47042,17 +46950,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -47077,7 +46985,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -47086,81 +46994,173 @@
         </is>
       </c>
       <c r="N267" t="n">
+        <v>0</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0</v>
+      </c>
+      <c r="P267" t="n">
+        <v>0</v>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ267" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK267" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM267" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN267" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT267" t="n">
         <v>2</v>
       </c>
-      <c r="O267" t="n">
-        <v>2</v>
-      </c>
-      <c r="R267" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S267" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO267" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP267" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR267" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr"/>
-      <c r="AT267" t="n">
-        <v>0</v>
-      </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47192,12 +47192,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -47222,7 +47222,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -47231,13 +47231,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O268" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R268" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -47270,42 +47270,42 @@
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47337,12 +47337,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47381,9 +47381,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="P269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -47392,77 +47389,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA269" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ269" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr"/>
       <c r="AT269" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47489,7 +47477,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -47541,98 +47529,18 @@
       <c r="P270" t="n">
         <v>0</v>
       </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R270" t="n">
+        <v>0</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD270" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE270" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI270" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ270" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN270" t="b">
-        <v>1</v>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
@@ -47726,17 +47634,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47761,90 +47669,182 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N271" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="P271" t="n">
+        <v>0</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN271" t="b">
         <v>1</v>
       </c>
-      <c r="O271" t="n">
-        <v>1</v>
-      </c>
-      <c r="R271" t="n">
-        <v>0.00367281181951979</v>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR271" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
       <c r="AT271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47876,12 +47876,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -47921,94 +47921,75 @@
         <v>1</v>
       </c>
       <c r="R272" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="AA272" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ272" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR272" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr"/>
       <c r="AT272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -48035,7 +48016,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -48084,98 +48065,23 @@
       <c r="O273" t="n">
         <v>1</v>
       </c>
+      <c r="R273" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U273" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1430</t>
         </is>
       </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1430</t>
-        </is>
-      </c>
-      <c r="W273" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X273" t="inlineStr">
-        <is>
-          <t>Meningococcus, total</t>
-        </is>
-      </c>
-      <c r="Y273" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z273" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB273" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD273" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE273" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF273" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG273" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ273" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK273" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM273" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN273" t="b">
-        <v>1</v>
       </c>
       <c r="AO273" t="inlineStr">
         <is>
@@ -48274,17 +48180,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -48318,81 +48224,175 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O274" t="n">
-        <v>0</v>
-      </c>
-      <c r="R274" t="n">
-        <v>0</v>
-      </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ274" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM274" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN274" t="b">
+        <v>1</v>
       </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR274" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS274" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
       <c r="AT274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48424,12 +48424,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -48476,87 +48476,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA275" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ275" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR275" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS275" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr"/>
       <c r="AT275" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -48583,7 +48564,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -48632,98 +48613,23 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
+      <c r="R276" t="n">
+        <v>0</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U276" t="inlineStr">
         <is>
           <t>SER_NO_FHI_707_MONTHLY</t>
         </is>
       </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_707_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W276" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X276" t="inlineStr">
-        <is>
-          <t>Syst. meningokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y276" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD276" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE276" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF276" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG276" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI276" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ276" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK276" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
-        </is>
-      </c>
-      <c r="AM276" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN276" t="b">
-        <v>1</v>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
@@ -48822,17 +48728,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -48857,7 +48763,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -48871,76 +48777,170 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
-      <c r="R277" t="n">
-        <v>0</v>
-      </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>Syst. meningokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic meningococcal category.</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN277" t="b">
+        <v>1</v>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR277" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_707_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -48972,12 +48972,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -49016,9 +49016,6 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="P278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -49027,77 +49024,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA278" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ278" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr"/>
       <c r="AT278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49124,7 +49112,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -49176,98 +49164,18 @@
       <c r="P279" t="n">
         <v>0</v>
       </c>
-      <c r="U279" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="V279" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
-        </is>
-      </c>
-      <c r="W279" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X279" t="inlineStr">
-        <is>
-          <t>Meningococcal Infection</t>
-        </is>
-      </c>
-      <c r="Y279" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z279" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R279" t="n">
+        <v>0</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB279" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC279" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD279" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE279" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF279" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG279" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI279" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ279" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK279" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM279" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN279" t="b">
-        <v>1</v>
       </c>
       <c r="AO279" t="inlineStr">
         <is>
@@ -49361,125 +49269,901 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0</v>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ280" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK280" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM280" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN280" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr">
+      <c r="F281" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
+      <c r="G281" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>D110</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>Meningococcal disease</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
         <is>
           <t>脑膜炎球菌病</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
+      <c r="K281" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
+      <c r="L281" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="M280" t="inlineStr">
+      <c r="M281" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N280" t="n">
+      <c r="N281" t="n">
         <v>4</v>
       </c>
-      <c r="O280" t="n">
+      <c r="O281" t="n">
         <v>4</v>
       </c>
-      <c r="R280" t="n">
+      <c r="R281" t="n">
         <v>0.001146015253107754</v>
       </c>
-      <c r="S280" t="inlineStr">
+      <c r="S281" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO280" t="inlineStr">
+      <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP280" t="inlineStr">
+      <c r="AP281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR280" t="inlineStr">
+      <c r="AR281" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS280" t="inlineStr"/>
-      <c r="AT280" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU280" t="inlineStr">
+      <c r="AS281" t="inlineStr"/>
+      <c r="AT281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU281" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV280" t="inlineStr">
+      <c r="AV281" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW280" t="inlineStr">
+      <c r="AW281" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX280" t="inlineStr">
+      <c r="AX281" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY280" t="inlineStr">
+      <c r="AY281" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ280" t="inlineStr">
+      <c r="AZ281" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA280" t="inlineStr">
+      <c r="BA281" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB280" t="inlineStr">
+      <c r="BB281" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC280" t="inlineStr">
+      <c r="BC281" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr"/>
+      <c r="AT282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
+      <c r="R283" t="n">
+        <v>0</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC283" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="P284" t="n">
+        <v>0</v>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ284" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK284" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM284" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN284" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -49516,7 +50200,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -49599,7 +50283,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
@@ -49609,7 +50293,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
@@ -49629,7 +50313,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -58735,13 +58735,13 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O328" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R328" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.0367281181951979</v>
       </c>
       <c r="S328" t="inlineStr">
         <is>
@@ -60984,6 +60984,1238 @@
       <c r="BC340" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N341" t="n">
+        <v>2</v>
+      </c>
+      <c r="O341" t="n">
+        <v>2</v>
+      </c>
+      <c r="R341" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO341" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP341" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR341" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS341" t="inlineStr"/>
+      <c r="AT341" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU341" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV341" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW341" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX341" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY341" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA341" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB341" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC341" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N342" t="n">
+        <v>0</v>
+      </c>
+      <c r="O342" t="n">
+        <v>0</v>
+      </c>
+      <c r="P342" t="n">
+        <v>0</v>
+      </c>
+      <c r="R342" t="n">
+        <v>0</v>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO342" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP342" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ342" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS342" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT342" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU342" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV342" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW342" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX342" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY342" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA342" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB342" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC342" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N343" t="n">
+        <v>0</v>
+      </c>
+      <c r="O343" t="n">
+        <v>0</v>
+      </c>
+      <c r="P343" t="n">
+        <v>0</v>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>Meningococcal Infection</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB343" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD343" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE343" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF343" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG343" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI343" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ343" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK343" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM343" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN343" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO343" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP343" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ343" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS343" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MENINGOCOCCAL_INFECTION; SER_SG_HIST_MENINGOCOCCAL_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT343" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU343" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV343" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW343" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX343" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY343" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA343" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB343" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC343" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N344" t="n">
+        <v>3</v>
+      </c>
+      <c r="O344" t="n">
+        <v>3</v>
+      </c>
+      <c r="R344" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO344" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP344" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR344" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS344" t="inlineStr"/>
+      <c r="AT344" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU344" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV344" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW344" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX344" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY344" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA344" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB344" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC344" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N345" t="n">
+        <v>0</v>
+      </c>
+      <c r="O345" t="n">
+        <v>0</v>
+      </c>
+      <c r="R345" t="n">
+        <v>0</v>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO345" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP345" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ345" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR345" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS345" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AT345" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU345" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV345" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW345" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX345" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY345" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA345" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB345" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC345" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N346" t="n">
+        <v>0</v>
+      </c>
+      <c r="O346" t="n">
+        <v>0</v>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>Meningococcus, total</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB346" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC346" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD346" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE346" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF346" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI346" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ346" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK346" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serogroup child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM346" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN346" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO346" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP346" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ346" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR346" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS346" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1430</t>
+        </is>
+      </c>
+      <c r="AT346" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU346" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV346" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW346" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX346" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY346" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA346" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB346" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC346" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N347" t="n">
+        <v>0</v>
+      </c>
+      <c r="O347" t="n">
+        <v>0</v>
+      </c>
+      <c r="R347" t="n">
+        <v>0</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO347" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP347" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR347" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS347" t="inlineStr"/>
+      <c r="AT347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU347" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV347" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW347" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX347" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY347" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA347" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB347" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC347" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -61020,7 +62252,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -61103,7 +62335,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -61113,7 +62345,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -61133,7 +62365,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
@@ -61165,7 +62397,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>440</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -58735,13 +58735,13 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O328" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R328" t="n">
-        <v>0.0367281181951979</v>
+        <v>0.04040093001471769</v>
       </c>
       <c r="S328" t="inlineStr">
         <is>
@@ -62397,7 +62397,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -20181,7 +20181,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -26436,7 +26436,7 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -36403,7 +36403,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -46041,7 +46041,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -54517,7 +54517,7 @@
       </c>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN304" t="b">
@@ -59684,7 +59684,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN333" t="b">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -70121,13 +70121,13 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O404" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R404" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S404" t="inlineStr">
         <is>
@@ -70377,7 +70377,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -72043,13 +72043,13 @@
         </is>
       </c>
       <c r="N410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R410" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S410" t="inlineStr">
         <is>
@@ -72857,7 +72857,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -72679,6 +72679,151 @@
         </is>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N414" t="n">
+        <v>0</v>
+      </c>
+      <c r="O414" t="n">
+        <v>0</v>
+      </c>
+      <c r="R414" t="n">
+        <v>0</v>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO414" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP414" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR414" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS414" t="inlineStr"/>
+      <c r="AT414" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU414" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV414" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW414" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX414" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY414" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA414" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB414" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC414" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -72712,7 +72857,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -72795,7 +72940,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -72805,7 +72950,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d110/2026-2029.xlsx
+++ b/diseases/d110/2026-2029.xlsx
@@ -5759,9 +5759,6 @@
       <c r="O31" t="n">
         <v>6</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -6454,9 +6451,6 @@
       <c r="O35" t="n">
         <v>3</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -7149,9 +7143,6 @@
       <c r="O39" t="n">
         <v>4</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -7844,9 +7835,6 @@
       <c r="O43" t="n">
         <v>5</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -12847,9 +12835,6 @@
       <c r="O72" t="n">
         <v>5</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -13542,9 +13527,6 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -14237,9 +14219,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -19554,9 +19533,6 @@
       <c r="O111" t="n">
         <v>2</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -20249,9 +20225,6 @@
       <c r="O115" t="n">
         <v>3</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -21639,9 +21612,6 @@
       <c r="O123" t="n">
         <v>8</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.002292030506215508</v>
       </c>
@@ -26243,9 +26213,6 @@
       <c r="O150" t="n">
         <v>3</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -26938,9 +26905,6 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -27633,9 +27597,6 @@
       <c r="O158" t="n">
         <v>2</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -28328,9 +28289,6 @@
       <c r="O162" t="n">
         <v>5</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -33716,9 +33674,6 @@
       <c r="O193" t="n">
         <v>3</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -34411,9 +34366,6 @@
       <c r="O197" t="n">
         <v>2</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -35106,9 +35058,6 @@
       <c r="O201" t="n">
         <v>3</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -35801,9 +35750,6 @@
       <c r="O205" t="n">
         <v>1</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -72821,6 +72767,156 @@
       <c r="BC414" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>meningococcal-disease</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N415" t="n">
+        <v>1</v>
+      </c>
+      <c r="O415" t="n">
+        <v>1</v>
+      </c>
+      <c r="R415" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA415" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO415" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP415" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR415" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS415" t="inlineStr"/>
+      <c r="AT415" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU415" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV415" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW415" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX415" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY415" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA415" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB415" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC415" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -72857,7 +72953,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -72940,7 +73036,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -72950,7 +73046,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11">
@@ -73002,7 +73098,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="16">
